--- a/vizualizare_date/sefgrupe.xlsx
+++ b/vizualizare_date/sefgrupe.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\VadimPK\Desktop\examsch\exam_app\vizualizare_date\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CF19BDD-9A3B-4BFB-A3CC-438F5E8F01BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7C10196-B4C9-47A7-8113-EE55B89B2C7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14355" yWindow="2955" windowWidth="13980" windowHeight="11115" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>id</t>
   </si>
@@ -37,12 +37,6 @@
     <t>phoneNumber</t>
   </si>
   <si>
-    <t>facultyName</t>
-  </si>
-  <si>
-    <t>departmentName</t>
-  </si>
-  <si>
     <t>Vadim</t>
   </si>
   <si>
@@ -52,19 +46,10 @@
     <t>vadim.orghian@student.usv.ro</t>
   </si>
   <si>
-    <t>FIESC</t>
-  </si>
-  <si>
-    <t>SIC</t>
-  </si>
-  <si>
-    <t>an</t>
-  </si>
-  <si>
-    <t>grupa</t>
-  </si>
-  <si>
-    <t>3712a</t>
+    <t>id_facultate</t>
+  </si>
+  <si>
+    <t>id_subgrupe</t>
   </si>
 </sst>
 </file>
@@ -146,7 +131,7 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -479,45 +464,35 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>12</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>7</v>
-      </c>
-      <c r="C2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>9</v>
       </c>
       <c r="E2">
         <v>123123</v>
       </c>
-      <c r="F2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I2">
+      <c r="F2">
         <v>1</v>
+      </c>
+      <c r="G2">
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/vizualizare_date/sefgrupe.xlsx
+++ b/vizualizare_date/sefgrupe.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\VadimPK\Desktop\examsch\exam_app\vizualizare_date\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7C10196-B4C9-47A7-8113-EE55B89B2C7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA88087A-2498-46A7-9DCF-071AC397118E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14355" yWindow="2955" windowWidth="13980" windowHeight="11115" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1620" yWindow="1320" windowWidth="13980" windowHeight="11100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="12">
   <si>
     <t>id</t>
   </si>
@@ -50,6 +50,12 @@
   </si>
   <si>
     <t>id_subgrupe</t>
+  </si>
+  <si>
+    <t>SefGrupaTest2</t>
+  </si>
+  <si>
+    <t>org@mail.ru</t>
   </si>
 </sst>
 </file>
@@ -437,7 +443,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="12.85546875" bestFit="1" customWidth="1"/>
@@ -495,9 +501,33 @@
         <v>29</v>
       </c>
     </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3">
+        <v>33</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>29</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="D2" r:id="rId1" xr:uid="{83A01EE0-3053-4544-9D09-9C99A5706E84}"/>
+    <hyperlink ref="D3" r:id="rId2" xr:uid="{D266B625-3EDA-4DF5-84DA-2B0D1712DEB0}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vizualizare_date/sefgrupe.xlsx
+++ b/vizualizare_date/sefgrupe.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\VadimPK\Desktop\examsch\exam_app\vizualizare_date\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA88087A-2498-46A7-9DCF-071AC397118E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03685FFE-09EF-42CC-8161-4F656939602D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1620" yWindow="1320" windowWidth="13980" windowHeight="11100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3945" yWindow="2055" windowWidth="20025" windowHeight="11100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -518,7 +518,7 @@
         <v>33</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G3">
         <v>29</v>
